--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487989_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487989_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.3464</v>
+        <v>13.4264</v>
       </c>
       <c r="E2" t="n">
-        <v>10.1295</v>
+        <v>10.2937</v>
       </c>
       <c r="F2" t="n">
-        <v>3.217</v>
+        <v>3.1327</v>
       </c>
       <c r="G2" t="n">
         <v>8.157299999999999</v>
@@ -610,13 +610,13 @@
         <v>3.1716</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2251</v>
+        <v>-0.145</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6936</v>
+        <v>-0.5293</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4685</v>
+        <v>0.3843</v>
       </c>
       <c r="V2" t="n">
         <v>4.2249</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6125</v>
+        <v>3.6572</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0635</v>
+        <v>0.0241</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5489</v>
+        <v>3.6332</v>
       </c>
       <c r="G3" t="n">
         <v>2.5822</v>
@@ -688,13 +688,13 @@
         <v>3.3698</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0907</v>
+        <v>-0.0459</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6936</v>
+        <v>-0.7331</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6029</v>
+        <v>0.6871</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2666</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8674</v>
+        <v>2.5295</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8405</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0269</v>
+        <v>1.8304</v>
       </c>
       <c r="G4" t="n">
         <v>0.3137</v>
@@ -766,13 +766,13 @@
         <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4416</v>
+        <v>0.1037</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3192</v>
+        <v>-0.4606</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7608</v>
+        <v>0.5642</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2666</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3213</v>
+        <v>1.3589</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0778</v>
+        <v>0.8345</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2436</v>
+        <v>0.5244</v>
       </c>
       <c r="G5" t="n">
         <v>1.4529</v>
@@ -844,13 +844,13 @@
         <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5102</v>
+        <v>-0.4726</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1176</v>
+        <v>-0.1257</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6278</v>
+        <v>-0.347</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2071</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARTIN GARCIA</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3701</v>
+        <v>0.3314</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9994</v>
+        <v>-2.1641</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6293</v>
+        <v>2.4955</v>
       </c>
       <c r="G7" t="n">
-        <v>1.556</v>
+        <v>-1.319</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1983</v>
+        <v>-0.0069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3577</v>
+        <v>-1.3121</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0691</v>
+        <v>-1.2067</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9887</v>
+        <v>1.0561</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0804</v>
+        <v>-2.2629</v>
       </c>
       <c r="M7" t="n">
-        <v>0.487</v>
+        <v>-0.1123</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2096</v>
+        <v>-1.0631</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2774</v>
+        <v>0.9508</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9911</v>
+        <v>2.3787</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5543</v>
+        <v>-0.2395</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9215</v>
+        <v>-0.3982</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3671</v>
+        <v>0.1587</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7403</v>
+        <v>2.4846</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7403</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>J. MARTIN GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1639</v>
+        <v>-0.0539</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0227</v>
+        <v>0.5754</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1866</v>
+        <v>-0.6293</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.319</v>
+        <v>1.556</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0069</v>
+        <v>1.1983</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3121</v>
+        <v>0.3577</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2067</v>
+        <v>1.0691</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0561</v>
+        <v>0.9887</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.2629</v>
+        <v>0.0804</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1123</v>
+        <v>0.487</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0631</v>
+        <v>0.2096</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9508</v>
+        <v>0.2774</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3787</v>
+        <v>0.9911</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.407</v>
+        <v>0.1303</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2568</v>
+        <v>0.4975</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1502</v>
+        <v>-0.3671</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4846</v>
+        <v>-1.7403</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0704</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7219</v>
+        <v>-1.192</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5692</v>
+        <v>-0.0463</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8473</v>
+        <v>-1.1457</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8936</v>
+        <v>0.3515</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3962</v>
+        <v>0.8297</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4974</v>
+        <v>-0.4782</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.2207</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3292</v>
+        <v>0.4105</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.639</v>
+        <v>-0.6312</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9255</v>
+        <v>0.5722</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.067</v>
+        <v>0.4193</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1415</v>
+        <v>0.1529</v>
       </c>
       <c r="P9" t="n">
         <v>0.3964</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4493</v>
+        <v>-0.4663</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9360000000000001</v>
+        <v>0.1744</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3852</v>
+        <v>-0.6407</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.674</v>
+        <v>-1.4737</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0965</v>
+        <v>-1.8655</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7823</v>
+        <v>-3.2636</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3142</v>
+        <v>1.3981</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3515</v>
+        <v>-1.8936</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8297</v>
+        <v>-1.3962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4782</v>
+        <v>-0.4974</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2207</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4105</v>
+        <v>-0.3292</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6312</v>
+        <v>-0.639</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5722</v>
+        <v>-0.9255</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4193</v>
+        <v>-1.067</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1529</v>
+        <v>0.1415</v>
       </c>
       <c r="P10" t="n">
         <v>0.3964</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3707</v>
+        <v>0.3056</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5616</v>
+        <v>-0.6304</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8092</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4737</v>
+        <v>-0.674</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6087</v>
+        <v>-2.4632</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6542</v>
+        <v>-2.0595</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0455</v>
+        <v>-0.4037</v>
       </c>
       <c r="G11" t="n">
         <v>0.0117</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1042</v>
+        <v>0.2496</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8112</v>
+        <v>-0.2165</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9153</v>
+        <v>0.4661</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3943</v>
+        <v>-2.6497</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1498</v>
+        <v>-3.7983</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7554999999999999</v>
+        <v>1.1486</v>
       </c>
       <c r="G12" t="n">
         <v>0.6136</v>
@@ -1390,13 +1390,13 @@
         <v>2.9733</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2062</v>
+        <v>-0.4616</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.756</v>
+        <v>-0.4045</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4502</v>
+        <v>-0.0571</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8107</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.405</v>
+        <v>-3.3758</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2766</v>
+        <v>-2.1912</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1284</v>
+        <v>-1.1846</v>
       </c>
       <c r="G13" t="n">
         <v>-1.3845</v>
@@ -1468,13 +1468,13 @@
         <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0888</v>
+        <v>-0.0596</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5064</v>
+        <v>-0.4211</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4176</v>
+        <v>0.3615</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.057900000000004</v>
+        <v>10.306</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.7414</v>
+        <v>-0.4934999999999992</v>
       </c>
       <c r="F14" t="n">
-        <v>10.7994</v>
+        <v>10.7996</v>
       </c>
       <c r="G14" t="n">
         <v>11.0445</v>
@@ -1546,13 +1546,13 @@
         <v>21.8045</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3493</v>
+        <v>-1.1013</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.4953</v>
+        <v>-3.2475</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1458</v>
+        <v>2.146</v>
       </c>
       <c r="V14" t="n">
         <v>-2.6105</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.37</v>
+        <v>2.8991</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1423</v>
+        <v>1.5311</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2276</v>
+        <v>1.368</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1129</v>
@@ -1624,13 +1624,13 @@
         <v>2.5769</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0151</v>
+        <v>0.5443</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4885</v>
+        <v>-0.1227</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5266</v>
+        <v>0.667</v>
       </c>
       <c r="V15" t="n">
         <v>5.0447</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3221</v>
+        <v>2.4124</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5747</v>
+        <v>-0.1383</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7473</v>
+        <v>2.5508</v>
       </c>
       <c r="G16" t="n">
         <v>2.7298</v>
@@ -1702,13 +1702,13 @@
         <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6712</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3599</v>
+        <v>-0.3532</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3113</v>
+        <v>1.1148</v>
       </c>
       <c r="V16" t="n">
         <v>-2.2684</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0768</v>
+        <v>2.3929</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4069</v>
+        <v>1.6107</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.7822</v>
       </c>
       <c r="G17" t="n">
         <v>1.1378</v>
@@ -1780,13 +1780,13 @@
         <v>0.3964</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0609</v>
+        <v>0.2551</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1248</v>
+        <v>0.0789</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0638</v>
+        <v>0.1762</v>
       </c>
       <c r="V17" t="n">
         <v>0.6036</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>A. OSORIO HERRERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.308</v>
+        <v>0.0871</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2898</v>
+        <v>-0.4207</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5978</v>
+        <v>0.5078</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5025</v>
+        <v>-0.3562</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0129</v>
+        <v>0.2771</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5153</v>
+        <v>-0.6333</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0618</v>
+        <v>-0.2959</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0189</v>
+        <v>0.343</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.957</v>
+        <v>-0.639</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5643</v>
+        <v>-0.0602</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.006</v>
+        <v>-0.066</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4417</v>
+        <v>0.0057</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.5769</v>
+        <v>0.5947</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.1538</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5769</v>
+        <v>0.5947</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1533</v>
+        <v>-0.1514</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1213</v>
+        <v>-0.1248</v>
       </c>
       <c r="U19" t="n">
-        <v>1.032</v>
+        <v>-0.0266</v>
       </c>
       <c r="V19" t="n">
-        <v>3.234</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. OSORIO HERRERA</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.059</v>
+        <v>-0.0185</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4207</v>
+        <v>-2.3917</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4797</v>
+        <v>2.3732</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3562</v>
+        <v>-1.5025</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2771</v>
+        <v>0.0129</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6333</v>
+        <v>-1.5153</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2959</v>
+        <v>0.0618</v>
       </c>
       <c r="K20" t="n">
-        <v>0.343</v>
+        <v>2.0189</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.639</v>
+        <v>-1.957</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0602</v>
+        <v>-1.5643</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.066</v>
+        <v>-2.006</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0057</v>
+        <v>0.4417</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5947</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-5.1538</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5947</v>
+        <v>2.5769</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1795</v>
+        <v>0.8268</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1248</v>
+        <v>0.0195</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0547</v>
+        <v>0.8074</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3.234</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.5532</v>
       </c>
     </row>
     <row r="21">
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.086</v>
+        <v>-1.3916</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7681</v>
+        <v>-2.0737</v>
       </c>
       <c r="F21" t="n">
         <v>0.6822</v>
@@ -2092,10 +2092,10 @@
         <v>0.9911</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4699</v>
+        <v>0.1643</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0072</v>
+        <v>-0.3128</v>
       </c>
       <c r="U21" t="n">
         <v>0.4771</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1066</v>
+        <v>-1.5245</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0754</v>
+        <v>0.7698</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1821</v>
+        <v>-2.2944</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9223</v>
@@ -2170,13 +2170,13 @@
         <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8245</v>
+        <v>0.4066</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9949</v>
+        <v>0.6893</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1704</v>
+        <v>-0.2827</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6036</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8468</v>
+        <v>-2.8843</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.374</v>
+        <v>-1.3553</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4728</v>
+        <v>-1.5289</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5466</v>
@@ -2248,13 +2248,13 @@
         <v>2.5769</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9038</v>
+        <v>0.0588</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1745</v>
+        <v>-0.1558</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2708</v>
+        <v>0.2146</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.99</v>
+        <v>-3.256</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1766</v>
+        <v>-2.6672</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8134</v>
+        <v>-0.5888</v>
       </c>
       <c r="G24" t="n">
         <v>-2.7493</v>
@@ -2326,13 +2326,13 @@
         <v>1.5858</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.091</v>
+        <v>-0.357</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8112</v>
+        <v>-0.3018</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2798</v>
+        <v>-0.0552</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7444</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ ANTUNEZ</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7098</v>
+        <v>-4.5958</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8724</v>
+        <v>-3.4068</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8374</v>
+        <v>-1.189</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.513</v>
+        <v>0.0404</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0005</v>
+        <v>-0.3096</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.5126</v>
+        <v>0.3499</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.9448</v>
+        <v>0.8714</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3303</v>
+        <v>0.1482</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.2751</v>
+        <v>0.7232</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.5682</v>
+        <v>-0.831</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3308</v>
+        <v>-0.4577</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2374</v>
+        <v>-0.3733</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1805</v>
+        <v>-3.1716</v>
       </c>
       <c r="R25" t="n">
-        <v>2.3787</v>
+        <v>2.1805</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3293</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5578</v>
+        <v>-1.1066</v>
       </c>
       <c r="U25" t="n">
-        <v>0.887</v>
+        <v>0.6</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-3.1385</v>
       </c>
       <c r="W25" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.5349</v>
+        <v>-3.1385</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>P. FERNANDEZ ANTUNEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.968</v>
+        <v>-4.6922</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6106</v>
+        <v>-3.7705</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3575</v>
+        <v>-0.9217</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0404</v>
+        <v>-4.513</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3096</v>
+        <v>-1.0005</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3499</v>
+        <v>-3.5126</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8714</v>
+        <v>-2.9448</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1482</v>
+        <v>0.3303</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7232</v>
+        <v>-3.2751</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.831</v>
+        <v>-1.5682</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4577</v>
+        <v>-1.3308</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3733</v>
+        <v>-0.2374</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.1716</v>
+        <v>-2.1805</v>
       </c>
       <c r="R26" t="n">
-        <v>2.1805</v>
+        <v>2.3787</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8788</v>
+        <v>0.3469</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.3103</v>
+        <v>-0.4559</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4315</v>
+        <v>0.8028</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.1385</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.1385</v>
+        <v>-2.5349</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.058</v>
+        <v>-9.0581</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.7996</v>
+        <v>-10.7993</v>
       </c>
       <c r="F27" t="n">
-        <v>1.741299999999999</v>
+        <v>1.741400000000001</v>
       </c>
       <c r="G27" t="n">
         <v>-11.0444</v>
@@ -2533,7 +2533,7 @@
         <v>-8.6577</v>
       </c>
       <c r="J27" t="n">
-        <v>1.698500000000001</v>
+        <v>1.6985</v>
       </c>
       <c r="K27" t="n">
         <v>6.5952</v>
@@ -2560,16 +2560,16 @@
         <v>18.8313</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3493</v>
+        <v>2.3494</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.146</v>
+        <v>-2.1459</v>
       </c>
       <c r="U27" t="n">
-        <v>4.4952</v>
+        <v>4.4954</v>
       </c>
       <c r="V27" t="n">
-        <v>2.610199999999999</v>
+        <v>2.6102</v>
       </c>
       <c r="W27" t="n">
         <v>11.4525</v>
